--- a/2026/ЗАВОДЫ/Останкино/ОПТы/01,26/14,01,29 Ост КИ ПРС/Заказ ЛП 18,01. ОптДонецк№9.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/ОПТы/01,26/14,01,29 Ост КИ ПРС/Заказ ЛП 18,01. ОптДонецк№9.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV_Poliakov_PRS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV_Poliakov_PRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A373F6-FFE0-4CD6-BCE5-036AF759AC47}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2248B64-FE41-4559-9C53-1DEC6F8CFE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,7 @@
     <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$591</definedName>
     <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$591</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1220,170 +1212,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1021080</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53499" name="Picture 7406">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FBD00000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:srcRect r="19516"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="449580" y="266700"/>
-          <a:ext cx="571500" cy="640080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1021080</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 7406">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:srcRect r="19516"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1059180" y="266700"/>
-          <a:ext cx="571500" cy="662940"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1021080</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 7406">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:srcRect r="19516"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1059180" y="266700"/>
-          <a:ext cx="571500" cy="662940"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
@@ -1925,14 +1753,14 @@
         <v>1001012486333</v>
       </c>
       <c r="E13" s="24">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="F13" s="23">
         <v>0.4</v>
       </c>
       <c r="G13" s="23">
         <f>E13*F13</f>
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H13" s="14">
         <v>3.2</v>
@@ -2029,14 +1857,14 @@
         <v>1001010106325</v>
       </c>
       <c r="E17" s="24">
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="F17" s="23">
         <v>0.4</v>
       </c>
       <c r="G17" s="23">
         <f>F17*E17</f>
-        <v>159.20000000000002</v>
+        <v>318.40000000000003</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
@@ -2113,14 +1941,14 @@
         <v>1001012637334</v>
       </c>
       <c r="E20" s="24">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F20" s="23">
         <v>0.4</v>
       </c>
       <c r="G20" s="23">
         <f>F20*E20</f>
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -2307,14 +2135,14 @@
         <v>1001012566392</v>
       </c>
       <c r="E27" s="24">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F27" s="23">
         <v>0.4</v>
       </c>
       <c r="G27" s="23">
         <f>E27*F27</f>
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="H27" s="14">
         <v>3.2</v>
@@ -2369,14 +2197,14 @@
         <v>1001012506353</v>
       </c>
       <c r="E29" s="24">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="F29" s="23">
         <v>0.4</v>
       </c>
       <c r="G29" s="23">
         <f>E29*F29</f>
-        <v>93.2</v>
+        <v>186.4</v>
       </c>
       <c r="H29" s="14">
         <v>3.2</v>
@@ -2917,14 +2745,14 @@
         <v>1001025176475</v>
       </c>
       <c r="E49" s="24">
-        <v>268</v>
+        <v>536</v>
       </c>
       <c r="F49" s="23">
         <v>0.4</v>
       </c>
       <c r="G49" s="23">
         <f>E49*F49</f>
-        <v>107.2</v>
+        <v>214.4</v>
       </c>
       <c r="H49" s="14">
         <v>2.4</v>
@@ -2950,14 +2778,14 @@
         <v>1001022246713</v>
       </c>
       <c r="E50" s="24">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F50" s="23">
         <v>0.41</v>
       </c>
       <c r="G50" s="23">
         <f>E50*F50</f>
-        <v>122.99999999999999</v>
+        <v>245.99999999999997</v>
       </c>
       <c r="H50" s="14">
         <v>3.28</v>
@@ -3148,14 +2976,14 @@
         <v>1001022657074</v>
       </c>
       <c r="E57" s="24">
-        <v>363</v>
+        <v>726</v>
       </c>
       <c r="F57" s="23">
         <v>0.6</v>
       </c>
       <c r="G57" s="23">
         <f>E57*F57</f>
-        <v>217.79999999999998</v>
+        <v>435.59999999999997</v>
       </c>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
@@ -3176,14 +3004,14 @@
         <v>1001025767284</v>
       </c>
       <c r="E58" s="24">
-        <v>253</v>
+        <v>506</v>
       </c>
       <c r="F58" s="23">
         <v>0.33</v>
       </c>
       <c r="G58" s="23">
         <f>E58*F58</f>
-        <v>83.490000000000009</v>
+        <v>166.98000000000002</v>
       </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
@@ -3286,14 +3114,14 @@
         <v>1001022467080</v>
       </c>
       <c r="E62" s="24">
-        <v>310</v>
+        <v>620</v>
       </c>
       <c r="F62" s="23">
         <v>0.41</v>
       </c>
       <c r="G62" s="23">
         <f>E62*F62</f>
-        <v>127.1</v>
+        <v>254.2</v>
       </c>
       <c r="H62" s="14">
         <v>4.0999999999999996</v>
@@ -3318,14 +3146,14 @@
         <v>1001022377066</v>
       </c>
       <c r="E63" s="24">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F63" s="23">
         <v>0.41</v>
       </c>
       <c r="G63" s="23">
         <f>E63*F63</f>
-        <v>122.99999999999999</v>
+        <v>245.99999999999997</v>
       </c>
       <c r="H63" s="14">
         <v>4.0999999999999996</v>
@@ -3624,14 +3452,14 @@
         <v>1001303637233</v>
       </c>
       <c r="E75" s="24">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F75" s="23">
         <v>0.31</v>
       </c>
       <c r="G75" s="23">
         <f>F75*E75</f>
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="H75" s="14"/>
       <c r="I75" s="14"/>
@@ -3764,14 +3592,14 @@
         <v>1001303107241</v>
       </c>
       <c r="E80" s="24">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="F80" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G80" s="23">
         <f t="shared" si="3"/>
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
@@ -4070,14 +3898,14 @@
         <v>1001300387154</v>
       </c>
       <c r="E91" s="24">
-        <v>252</v>
+        <v>504</v>
       </c>
       <c r="F91" s="23">
         <v>0.35</v>
       </c>
       <c r="G91" s="23">
         <f>E91*F91</f>
-        <v>88.199999999999989</v>
+        <v>176.39999999999998</v>
       </c>
       <c r="H91" s="14"/>
       <c r="I91" s="14"/>
@@ -4422,14 +4250,14 @@
         <v>1001302347177</v>
       </c>
       <c r="E104" s="24">
-        <v>212</v>
+        <v>424</v>
       </c>
       <c r="F104" s="23">
         <v>0.35</v>
       </c>
       <c r="G104" s="23">
         <f t="shared" si="5"/>
-        <v>74.199999999999989</v>
+        <v>148.39999999999998</v>
       </c>
       <c r="H104" s="14"/>
       <c r="I104" s="14"/>
@@ -4721,14 +4549,14 @@
         <v>1001203146834</v>
       </c>
       <c r="E115" s="24">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F115" s="75">
         <v>0.1</v>
       </c>
       <c r="G115" s="23">
         <f>E115*F115</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H115" s="78">
         <v>1</v>
@@ -4941,14 +4769,14 @@
         <v>1001063106937</v>
       </c>
       <c r="E123" s="24">
-        <v>166</v>
+        <v>332</v>
       </c>
       <c r="F123" s="23">
         <v>0.25</v>
       </c>
       <c r="G123" s="23">
         <f>E123*F123</f>
-        <v>41.5</v>
+        <v>83</v>
       </c>
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
@@ -4969,14 +4797,14 @@
         <v>1001203117382</v>
       </c>
       <c r="E124" s="24">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F124" s="23">
         <v>0.12</v>
       </c>
       <c r="G124" s="23">
         <f>E124*F124</f>
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H124" s="14">
         <v>0.96</v>
@@ -5083,14 +4911,14 @@
         <v>1001062505483</v>
       </c>
       <c r="E128" s="24">
-        <v>187</v>
+        <v>374</v>
       </c>
       <c r="F128" s="23">
         <v>0.25</v>
       </c>
       <c r="G128" s="23">
         <f t="shared" ref="G128:G133" si="7">E128*F128</f>
-        <v>46.75</v>
+        <v>93.5</v>
       </c>
       <c r="H128" s="14">
         <v>2</v>
@@ -5171,14 +4999,14 @@
         <v>1001060755931</v>
       </c>
       <c r="E131" s="24">
-        <v>344</v>
+        <v>688</v>
       </c>
       <c r="F131" s="23">
         <v>0.22</v>
       </c>
       <c r="G131" s="23">
         <f t="shared" si="7"/>
-        <v>75.680000000000007</v>
+        <v>151.36000000000001</v>
       </c>
       <c r="H131" s="14"/>
       <c r="I131" s="14"/>
@@ -5225,14 +5053,14 @@
         <v>1001205376221</v>
       </c>
       <c r="E133" s="24">
-        <v>211</v>
+        <v>422</v>
       </c>
       <c r="F133" s="23">
         <v>0.09</v>
       </c>
       <c r="G133" s="23">
         <f t="shared" si="7"/>
-        <v>18.989999999999998</v>
+        <v>37.979999999999997</v>
       </c>
       <c r="H133" s="14"/>
       <c r="I133" s="14"/>
@@ -5324,14 +5152,14 @@
         <v>1001094053215</v>
       </c>
       <c r="E137" s="24">
-        <v>144</v>
+        <v>288</v>
       </c>
       <c r="F137" s="23">
         <v>0.4</v>
       </c>
       <c r="G137" s="23">
         <f>E137*F137</f>
-        <v>57.6</v>
+        <v>115.2</v>
       </c>
       <c r="H137" s="14">
         <v>3.2</v>
@@ -5615,14 +5443,14 @@
         <v>1001225416228</v>
       </c>
       <c r="E148" s="24">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F148" s="23">
         <v>0.09</v>
       </c>
       <c r="G148" s="23">
         <f t="shared" si="9"/>
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="H148" s="14"/>
       <c r="I148" s="14"/>
@@ -5643,14 +5471,14 @@
         <v>1001205386222</v>
       </c>
       <c r="E149" s="24">
-        <v>289</v>
+        <v>578</v>
       </c>
       <c r="F149" s="23">
         <v>0.09</v>
       </c>
       <c r="G149" s="23">
         <f t="shared" si="9"/>
-        <v>26.009999999999998</v>
+        <v>52.019999999999996</v>
       </c>
       <c r="H149" s="14"/>
       <c r="I149" s="14"/>
@@ -5671,14 +5499,14 @@
         <v>1001225406754</v>
       </c>
       <c r="E150" s="24">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="F150" s="23">
         <v>0.09</v>
       </c>
       <c r="G150" s="23">
         <f t="shared" si="9"/>
-        <v>31.5</v>
+        <v>63</v>
       </c>
       <c r="H150" s="14"/>
       <c r="I150" s="14"/>
@@ -5729,14 +5557,14 @@
         <v>1001220226208</v>
       </c>
       <c r="E152" s="24">
-        <v>209</v>
+        <v>418</v>
       </c>
       <c r="F152" s="23">
         <v>0.15</v>
       </c>
       <c r="G152" s="23">
         <f>F152*E152</f>
-        <v>31.349999999999998</v>
+        <v>62.699999999999996</v>
       </c>
       <c r="H152" s="14"/>
       <c r="I152" s="14"/>
@@ -5781,14 +5609,14 @@
         <v>1001223297103</v>
       </c>
       <c r="E154" s="24">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F154" s="75">
         <v>0.18</v>
       </c>
       <c r="G154" s="23">
         <f>E154*F154</f>
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="H154" s="76">
         <v>1.8</v>
@@ -5808,12 +5636,12 @@
       <c r="D155" s="38"/>
       <c r="E155" s="17">
         <f>SUM(E10:E154)</f>
-        <v>6489</v>
+        <v>12978</v>
       </c>
       <c r="F155" s="17"/>
       <c r="G155" s="17">
         <f>SUM(G11:G154)</f>
-        <v>1982.27</v>
+        <v>3964.54</v>
       </c>
       <c r="H155" s="17"/>
       <c r="I155" s="17"/>
@@ -21067,6 +20895,5 @@
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="17" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>